--- a/jogos_2026-09-29.xlsx
+++ b/jogos_2026-09-29.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q3">
         <v>0</v>

--- a/jogos_2026-09-29.xlsx
+++ b/jogos_2026-09-29.xlsx
@@ -970,55 +970,55 @@
         <v>10.5</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/jogos_2026-09-29.xlsx
+++ b/jogos_2026-09-29.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O2">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="P2">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q2">
         <v>2.73</v>
@@ -650,49 +650,49 @@
         <v>2.1</v>
       </c>
       <c r="S2">
+        <v>1.41</v>
+      </c>
+      <c r="T2">
+        <v>2.97</v>
+      </c>
+      <c r="U2">
+        <v>2.75</v>
+      </c>
+      <c r="V2">
         <v>1.38</v>
       </c>
-      <c r="T2">
-        <v>2.6</v>
-      </c>
-      <c r="U2">
-        <v>2.83</v>
-      </c>
-      <c r="V2">
-        <v>1.34</v>
-      </c>
       <c r="W2">
+        <v>1.04</v>
+      </c>
+      <c r="X2">
         <v>1.06</v>
       </c>
-      <c r="X2">
-        <v>1.05</v>
-      </c>
       <c r="Y2">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AA2">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB2">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC2">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AD2">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE2">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF2">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG2">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.27</v>
       </c>
       <c r="AK2">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -976,7 +976,7 @@
         <v>2.63</v>
       </c>
       <c r="S4">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T4">
         <v>3.5</v>
@@ -988,7 +988,7 @@
         <v>1.56</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X4">
         <v>1.02</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AK4">
         <v>3.86</v>

--- a/jogos_2026-09-29.xlsx
+++ b/jogos_2026-09-29.xlsx
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.26</v>
+        <v>2.01</v>
       </c>
       <c r="O3">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -973,7 +973,7 @@
         <v>1.65</v>
       </c>
       <c r="R4">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="S4">
         <v>1.25</v>
@@ -1000,10 +1000,10 @@
         <v>4.25</v>
       </c>
       <c r="AA4">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB4">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC4">
         <v>2.41</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AK4">
         <v>3.86</v>

--- a/jogos_2026-09-29.xlsx
+++ b/jogos_2026-09-29.xlsx
@@ -988,7 +988,7 @@
         <v>1.56</v>
       </c>
       <c r="W4">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
         <v>1.02</v>

--- a/jogos_2026-09-29.xlsx
+++ b/jogos_2026-09-29.xlsx
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="O3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P3">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="Q3">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="R3">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U3">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="V3">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X3">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y3">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="Z3">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA3">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB3">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AC3">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AD3">
         <v>1.2</v>
       </c>
       <c r="AE3">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG3">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.29</v>
       </c>
       <c r="AK3">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/jogos_2026-09-29.xlsx
+++ b/jogos_2026-09-29.xlsx
@@ -801,16 +801,16 @@
         <v>2.03</v>
       </c>
       <c r="O3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P3">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="Q3">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S3">
         <v>1.4</v>
@@ -819,10 +819,10 @@
         <v>2.75</v>
       </c>
       <c r="U3">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="V3">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="W3">
         <v>1.04</v>
@@ -852,10 +852,10 @@
         <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG3">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="O4">
-        <v>5.6</v>
+        <v>5.25</v>
       </c>
       <c r="P4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="R4">
-        <v>2.53</v>
+        <v>2.83</v>
       </c>
       <c r="S4">
         <v>1.25</v>
@@ -1000,10 +1000,10 @@
         <v>4.25</v>
       </c>
       <c r="AA4">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB4">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC4">
         <v>2.41</v>

--- a/jogos_2026-09-29.xlsx
+++ b/jogos_2026-09-29.xlsx
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="O3">
         <v>3.2</v>
       </c>
       <c r="P3">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="Q3">
         <v>2.7</v>
       </c>
       <c r="R3">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
         <v>1.4</v>
@@ -819,10 +819,10 @@
         <v>2.75</v>
       </c>
       <c r="U3">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="V3">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="W3">
         <v>1.04</v>
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="O4">
-        <v>5.25</v>
+        <v>6.4</v>
       </c>
       <c r="P4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q4">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="R4">
-        <v>2.83</v>
+        <v>2.53</v>
       </c>
       <c r="S4">
         <v>1.25</v>
       </c>
       <c r="T4">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U4">
         <v>2.23</v>
@@ -988,7 +988,7 @@
         <v>1.56</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X4">
         <v>1.02</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AK4">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/jogos_2026-09-29.xlsx
+++ b/jogos_2026-09-29.xlsx
@@ -635,25 +635,25 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O2">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P2">
         <v>3.1</v>
       </c>
       <c r="Q2">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="R2">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S2">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="T2">
-        <v>2.97</v>
+        <v>2.77</v>
       </c>
       <c r="U2">
         <v>2.75</v>
@@ -662,7 +662,7 @@
         <v>1.38</v>
       </c>
       <c r="W2">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
         <v>1.06</v>
@@ -671,7 +671,7 @@
         <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA2">
         <v>2</v>
@@ -689,7 +689,7 @@
         <v>1.08</v>
       </c>
       <c r="AF2">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG2">
         <v>1.95</v>
@@ -840,7 +840,7 @@
         <v>2.2</v>
       </c>
       <c r="AB3">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC3">
         <v>4</v>

--- a/jogos_2026-09-29.xlsx
+++ b/jogos_2026-09-29.xlsx
@@ -961,22 +961,22 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="O4">
-        <v>6.4</v>
+        <v>5.55</v>
       </c>
       <c r="P4">
         <v>11</v>
       </c>
       <c r="Q4">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="R4">
         <v>2.53</v>
       </c>
       <c r="S4">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T4">
         <v>3.8</v>
@@ -1034,7 +1034,7 @@
         <v>1</v>
       </c>
       <c r="AK4">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/jogos_2026-09-29.xlsx
+++ b/jogos_2026-09-29.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N2">
@@ -644,16 +644,16 @@
         <v>3.1</v>
       </c>
       <c r="Q2">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="R2">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="U2">
         <v>2.75</v>
@@ -662,7 +662,7 @@
         <v>1.38</v>
       </c>
       <c r="W2">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
         <v>1.06</v>
@@ -674,7 +674,7 @@
         <v>3.5</v>
       </c>
       <c r="AA2">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB2">
         <v>1.75</v>
@@ -689,7 +689,7 @@
         <v>1.08</v>
       </c>
       <c r="AF2">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG2">
         <v>1.95</v>

--- a/jogos_2026-09-29.xlsx
+++ b/jogos_2026-09-29.xlsx
@@ -692,7 +692,7 @@
         <v>1.75</v>
       </c>
       <c r="AG2">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="O3">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
-        <v>3.34</v>
+        <v>2.83</v>
       </c>
       <c r="Q3">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="S3">
         <v>1.4</v>
@@ -819,22 +819,22 @@
         <v>2.75</v>
       </c>
       <c r="U3">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V3">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y3">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z3">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AA3">
         <v>2.2</v>
@@ -852,10 +852,10 @@
         <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG3">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,31 +961,31 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="O4">
-        <v>5.55</v>
+        <v>5.15</v>
       </c>
       <c r="P4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="R4">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="S4">
         <v>1.29</v>
       </c>
       <c r="T4">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="U4">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="V4">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="W4">
         <v>1.12</v>
@@ -994,32 +994,32 @@
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z4">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AA4">
+        <v>1.66</v>
+      </c>
+      <c r="AB4">
+        <v>2.15</v>
+      </c>
+      <c r="AC4">
+        <v>2.52</v>
+      </c>
+      <c r="AD4">
+        <v>1.41</v>
+      </c>
+      <c r="AE4">
+        <v>1.13</v>
+      </c>
+      <c r="AF4">
+        <v>2.15</v>
+      </c>
+      <c r="AG4">
         <v>1.61</v>
       </c>
-      <c r="AB4">
-        <v>2.25</v>
-      </c>
-      <c r="AC4">
-        <v>2.41</v>
-      </c>
-      <c r="AD4">
-        <v>1.45</v>
-      </c>
-      <c r="AE4">
-        <v>1.15</v>
-      </c>
-      <c r="AF4">
-        <v>2.2</v>
-      </c>
-      <c r="AG4">
-        <v>1.6</v>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AK4">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/jogos_2026-09-29.xlsx
+++ b/jogos_2026-09-29.xlsx
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -624,14 +624,14 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -641,7 +641,7 @@
         <v>3.2</v>
       </c>
       <c r="P2">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q2">
         <v>2.73</v>
@@ -674,7 +674,7 @@
         <v>3.5</v>
       </c>
       <c r="AA2">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AB2">
         <v>1.75</v>
@@ -696,7 +696,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         <v>2.83</v>
       </c>
       <c r="Q3">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="R3">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="S3">
         <v>1.4</v>
@@ -822,37 +822,37 @@
         <v>3</v>
       </c>
       <c r="V3">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
+        <v>1.02</v>
+      </c>
+      <c r="X3">
         <v>1.05</v>
       </c>
-      <c r="X3">
-        <v>1.08</v>
-      </c>
       <c r="Y3">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z3">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="AA3">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB3">
         <v>1.65</v>
       </c>
       <c r="AC3">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="AD3">
         <v>1.2</v>
       </c>
       <c r="AE3">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF3">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AG3">
         <v>1.85</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK3">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/jogos_2026-09-29.xlsx
+++ b/jogos_2026-09-29.xlsx
@@ -807,10 +807,10 @@
         <v>2.83</v>
       </c>
       <c r="Q3">
-        <v>3.04</v>
+        <v>2.91</v>
       </c>
       <c r="R3">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="S3">
         <v>1.4</v>
@@ -819,7 +819,7 @@
         <v>2.75</v>
       </c>
       <c r="U3">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="V3">
         <v>1.36</v>
@@ -828,34 +828,34 @@
         <v>1.02</v>
       </c>
       <c r="X3">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z3">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AA3">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AB3">
         <v>1.65</v>
       </c>
       <c r="AC3">
-        <v>3.92</v>
+        <v>3.74</v>
       </c>
       <c r="AD3">
         <v>1.2</v>
       </c>
       <c r="AE3">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF3">
         <v>1.82</v>
       </c>
       <c r="AG3">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK3">
         <v>1.62</v>

--- a/jogos_2026-09-29.xlsx
+++ b/jogos_2026-09-29.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="O4">
-        <v>5.15</v>
+        <v>5.45</v>
       </c>
       <c r="P4">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q4">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="R4">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="S4">
         <v>1.29</v>
@@ -982,10 +982,10 @@
         <v>3.4</v>
       </c>
       <c r="U4">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="V4">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W4">
         <v>1.12</v>
@@ -994,31 +994,31 @@
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z4">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AA4">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AB4">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC4">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="AD4">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AE4">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF4">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AG4">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.01</v>
       </c>
       <c r="AK4">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/jogos_2026-09-29.xlsx
+++ b/jogos_2026-09-29.xlsx
@@ -961,31 +961,31 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="O4">
-        <v>5.45</v>
+        <v>5.7</v>
       </c>
       <c r="P4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q4">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="R4">
-        <v>2.67</v>
+        <v>2.74</v>
       </c>
       <c r="S4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U4">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V4">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W4">
         <v>1.12</v>
@@ -994,31 +994,31 @@
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z4">
-        <v>3.98</v>
+        <v>4.17</v>
       </c>
       <c r="AA4">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB4">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC4">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="AD4">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AE4">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF4">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AG4">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK4">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AL4">
         <v>0</v>
